--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.83812558631267</v>
+      </c>
+      <c r="C2">
         <v>22.05875783611537</v>
-      </c>
-      <c r="C2">
-        <v>27.83812558631267</v>
       </c>
       <c r="D2">
         <v>4.533346834075874</v>
       </c>
       <c r="E2">
+        <v>18.57151726621385</v>
+      </c>
+      <c r="F2">
+        <v>66.71252778364149</v>
+      </c>
+      <c r="G2">
         <v>14.71595495014466</v>
-      </c>
-      <c r="F2">
-        <v>66.71252778364148</v>
-      </c>
-      <c r="G2">
-        <v>18.57151726621385</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.87157732356344</v>
+      </c>
+      <c r="C3">
         <v>20.40107983031238</v>
-      </c>
-      <c r="C3">
-        <v>30.87157732356344</v>
       </c>
       <c r="D3">
         <v>4.901701323251418</v>
       </c>
       <c r="E3">
+        <v>20.40790312300829</v>
+      </c>
+      <c r="F3">
+        <v>66.10579987253028</v>
+      </c>
+      <c r="G3">
         <v>13.48629700446144</v>
-      </c>
-      <c r="F3">
-        <v>66.10579987253027</v>
-      </c>
-      <c r="G3">
-        <v>20.40790312300828</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>38.51851851851852</v>
+      </c>
+      <c r="C4">
         <v>16.2962962962963</v>
-      </c>
-      <c r="C4">
-        <v>38.51851851851852</v>
       </c>
       <c r="D4">
         <v>6.136363636363637</v>
       </c>
       <c r="E4">
-        <v>10.52631578947368</v>
+        <v>24.88038277511961</v>
       </c>
       <c r="F4">
         <v>64.59330143540669</v>
       </c>
       <c r="G4">
-        <v>24.88038277511961</v>
+        <v>10.52631578947368</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.89250493096647</v>
+      </c>
+      <c r="C5">
         <v>30.43639053254438</v>
-      </c>
-      <c r="C5">
-        <v>30.89250493096647</v>
       </c>
       <c r="D5">
         <v>3.285540704738761</v>
       </c>
       <c r="E5">
-        <v>18.86605027890273</v>
+        <v>19.14877359211431</v>
       </c>
       <c r="F5">
         <v>61.98517612898296</v>
       </c>
       <c r="G5">
-        <v>19.14877359211431</v>
+        <v>18.86605027890273</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.39071276994133</v>
+      </c>
+      <c r="C6">
         <v>19.81858278200807</v>
-      </c>
-      <c r="C6">
-        <v>30.39071276994133</v>
       </c>
       <c r="D6">
         <v>5.045769473021205</v>
       </c>
       <c r="E6">
-        <v>13.19397891401061</v>
+        <v>20.23224505398922</v>
       </c>
       <c r="F6">
         <v>66.57377603200018</v>
       </c>
       <c r="G6">
-        <v>20.23224505398922</v>
+        <v>13.19397891401061</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.28571428571428</v>
+      </c>
+      <c r="C7">
         <v>22.14285714285714</v>
-      </c>
-      <c r="C7">
-        <v>29.28571428571428</v>
       </c>
       <c r="D7">
         <v>4.516129032258065</v>
       </c>
       <c r="E7">
-        <v>14.62264150943396</v>
+        <v>19.33962264150944</v>
       </c>
       <c r="F7">
         <v>66.0377358490566</v>
       </c>
       <c r="G7">
-        <v>19.33962264150944</v>
+        <v>14.62264150943396</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>32.33207547169811</v>
+      </c>
+      <c r="C8">
         <v>17.20754716981132</v>
-      </c>
-      <c r="C8">
-        <v>32.33207547169811</v>
       </c>
       <c r="D8">
         <v>5.81140350877193</v>
       </c>
       <c r="E8">
-        <v>11.50701524174826</v>
+        <v>21.62107600686383</v>
       </c>
       <c r="F8">
         <v>66.87190875138791</v>
       </c>
       <c r="G8">
-        <v>21.62107600686383</v>
+        <v>11.50701524174826</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.05162035629598</v>
+      </c>
+      <c r="C9">
         <v>30.74116860217669</v>
-      </c>
-      <c r="C9">
-        <v>33.05162035629598</v>
       </c>
       <c r="D9">
         <v>3.252966772151899</v>
       </c>
       <c r="E9">
-        <v>18.7683284457478</v>
+        <v>20.17892275140132</v>
       </c>
       <c r="F9">
         <v>61.05274880285089</v>
       </c>
       <c r="G9">
-        <v>20.17892275140132</v>
+        <v>18.7683284457478</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.81720430107527</v>
+      </c>
+      <c r="C10">
         <v>22.79569892473118</v>
-      </c>
-      <c r="C10">
-        <v>28.81720430107527</v>
       </c>
       <c r="D10">
         <v>4.386792452830188</v>
       </c>
       <c r="E10">
-        <v>15.0354609929078</v>
+        <v>19.00709219858156</v>
       </c>
       <c r="F10">
         <v>65.95744680851064</v>
       </c>
       <c r="G10">
-        <v>19.00709219858156</v>
+        <v>15.0354609929078</v>
       </c>
     </row>
   </sheetData>
